--- a/artfynd/A 15371-2026 artfynd.xlsx
+++ b/artfynd/A 15371-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131949850</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>131950773</v>
       </c>
       <c r="B3" t="n">
-        <v>80421</v>
+        <v>80423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131959466</v>
       </c>
       <c r="B4" t="n">
-        <v>80421</v>
+        <v>80423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131949502</v>
+        <v>131949493</v>
       </c>
       <c r="B5" t="n">
-        <v>80420</v>
+        <v>80423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,34 +1003,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401764</v>
+        <v>401759</v>
       </c>
       <c r="R5" t="n">
-        <v>7045490</v>
+        <v>7045486</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131949493</v>
+        <v>131949502</v>
       </c>
       <c r="B6" t="n">
-        <v>80421</v>
+        <v>80422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401759</v>
+        <v>401764</v>
       </c>
       <c r="R6" t="n">
-        <v>7045486</v>
+        <v>7045490</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,7 +1209,7 @@
         <v>131953014</v>
       </c>
       <c r="B7" t="n">
-        <v>80421</v>
+        <v>80423</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131952947</v>
+        <v>131952934</v>
       </c>
       <c r="B11" t="n">
-        <v>80421</v>
+        <v>57948</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401736</v>
+        <v>401733</v>
       </c>
       <c r="R11" t="n">
-        <v>7045554</v>
+        <v>7045548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1719,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131952934</v>
+        <v>131952947</v>
       </c>
       <c r="B12" t="n">
-        <v>57948</v>
+        <v>80423</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,21 +1762,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1786,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401733</v>
+        <v>401736</v>
       </c>
       <c r="R12" t="n">
-        <v>7045548</v>
+        <v>7045554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1821,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1826,12 +1831,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 15371-2026 artfynd.xlsx
+++ b/artfynd/A 15371-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131949850</v>
+        <v>131950773</v>
       </c>
       <c r="B2" t="n">
-        <v>91912</v>
+        <v>80423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>401779</v>
+        <v>401771</v>
       </c>
       <c r="R2" t="n">
-        <v>7045486</v>
+        <v>7045463</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -741,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131950773</v>
+        <v>131949850</v>
       </c>
       <c r="B3" t="n">
-        <v>80423</v>
+        <v>91912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,23 +793,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401771</v>
+        <v>401779</v>
       </c>
       <c r="R3" t="n">
-        <v>7045463</v>
+        <v>7045486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,7 +848,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 15371-2026 artfynd.xlsx
+++ b/artfynd/A 15371-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131950773</v>
+        <v>131949850</v>
       </c>
       <c r="B2" t="n">
-        <v>80423</v>
+        <v>91912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>401771</v>
+        <v>401779</v>
       </c>
       <c r="R2" t="n">
-        <v>7045463</v>
+        <v>7045486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +741,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +751,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131949850</v>
+        <v>131950773</v>
       </c>
       <c r="B3" t="n">
-        <v>91912</v>
+        <v>80423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,19 +789,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401779</v>
+        <v>401771</v>
       </c>
       <c r="R3" t="n">
-        <v>7045486</v>
+        <v>7045463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,7 +848,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 15371-2026 artfynd.xlsx
+++ b/artfynd/A 15371-2026 artfynd.xlsx
@@ -992,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131949493</v>
+        <v>131949502</v>
       </c>
       <c r="B5" t="n">
-        <v>80423</v>
+        <v>80422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,34 +1003,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401759</v>
+        <v>401764</v>
       </c>
       <c r="R5" t="n">
-        <v>7045486</v>
+        <v>7045490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131949502</v>
+        <v>131949493</v>
       </c>
       <c r="B6" t="n">
-        <v>80422</v>
+        <v>80423</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401764</v>
+        <v>401759</v>
       </c>
       <c r="R6" t="n">
-        <v>7045490</v>
+        <v>7045486</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131952934</v>
+        <v>131952947</v>
       </c>
       <c r="B11" t="n">
-        <v>57948</v>
+        <v>80423</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401733</v>
+        <v>401736</v>
       </c>
       <c r="R11" t="n">
-        <v>7045548</v>
+        <v>7045554</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,12 +1719,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1751,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131952947</v>
+        <v>131952934</v>
       </c>
       <c r="B12" t="n">
-        <v>80423</v>
+        <v>57948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1786,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401736</v>
+        <v>401733</v>
       </c>
       <c r="R12" t="n">
-        <v>7045554</v>
+        <v>7045548</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,7 +1816,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1831,7 +1826,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 15371-2026 artfynd.xlsx
+++ b/artfynd/A 15371-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131949850</v>
+        <v>131950773</v>
       </c>
       <c r="B2" t="n">
-        <v>91912</v>
+        <v>80423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>401779</v>
+        <v>401771</v>
       </c>
       <c r="R2" t="n">
-        <v>7045486</v>
+        <v>7045463</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -741,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131950773</v>
+        <v>131949850</v>
       </c>
       <c r="B3" t="n">
-        <v>80423</v>
+        <v>91912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,23 +793,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401771</v>
+        <v>401779</v>
       </c>
       <c r="R3" t="n">
-        <v>7045463</v>
+        <v>7045486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,7 +848,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -992,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131949502</v>
+        <v>131949493</v>
       </c>
       <c r="B5" t="n">
-        <v>80422</v>
+        <v>80423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,34 +1003,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401764</v>
+        <v>401759</v>
       </c>
       <c r="R5" t="n">
-        <v>7045490</v>
+        <v>7045486</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131949493</v>
+        <v>131949502</v>
       </c>
       <c r="B6" t="n">
-        <v>80423</v>
+        <v>80422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401759</v>
+        <v>401764</v>
       </c>
       <c r="R6" t="n">
-        <v>7045486</v>
+        <v>7045490</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 15371-2026 artfynd.xlsx
+++ b/artfynd/A 15371-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131949850</v>
       </c>
       <c r="B2" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>131950773</v>
       </c>
       <c r="B3" t="n">
-        <v>80423</v>
+        <v>80425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131959466</v>
       </c>
       <c r="B4" t="n">
-        <v>80423</v>
+        <v>80425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131949493</v>
+        <v>131949502</v>
       </c>
       <c r="B5" t="n">
-        <v>80423</v>
+        <v>80424</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,34 +1003,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401759</v>
+        <v>401764</v>
       </c>
       <c r="R5" t="n">
-        <v>7045486</v>
+        <v>7045490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131949502</v>
+        <v>131949493</v>
       </c>
       <c r="B6" t="n">
-        <v>80422</v>
+        <v>80425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401764</v>
+        <v>401759</v>
       </c>
       <c r="R6" t="n">
-        <v>7045490</v>
+        <v>7045486</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,7 +1209,7 @@
         <v>131953014</v>
       </c>
       <c r="B7" t="n">
-        <v>80423</v>
+        <v>80425</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>131950316</v>
       </c>
       <c r="B8" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131951992</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>131951700</v>
       </c>
       <c r="B10" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>131952947</v>
       </c>
       <c r="B11" t="n">
-        <v>80423</v>
+        <v>80425</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>131952934</v>
       </c>
       <c r="B12" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>131952639</v>
       </c>
       <c r="B13" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 15371-2026 artfynd.xlsx
+++ b/artfynd/A 15371-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131949850</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>131950773</v>
       </c>
       <c r="B3" t="n">
-        <v>80425</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131959466</v>
       </c>
       <c r="B4" t="n">
-        <v>80425</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131949502</v>
+        <v>131949493</v>
       </c>
       <c r="B5" t="n">
-        <v>80424</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,34 +1003,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401764</v>
+        <v>401759</v>
       </c>
       <c r="R5" t="n">
-        <v>7045490</v>
+        <v>7045486</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131949493</v>
+        <v>131949502</v>
       </c>
       <c r="B6" t="n">
-        <v>80425</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401759</v>
+        <v>401764</v>
       </c>
       <c r="R6" t="n">
-        <v>7045486</v>
+        <v>7045490</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,7 +1209,7 @@
         <v>131953014</v>
       </c>
       <c r="B7" t="n">
-        <v>80425</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>131950316</v>
       </c>
       <c r="B8" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131951992</v>
       </c>
       <c r="B9" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>131951700</v>
       </c>
       <c r="B10" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>131952947</v>
       </c>
       <c r="B11" t="n">
-        <v>80425</v>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>131952934</v>
       </c>
       <c r="B12" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>131952639</v>
       </c>
       <c r="B13" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 15371-2026 artfynd.xlsx
+++ b/artfynd/A 15371-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131949850</v>
+        <v>131950773</v>
       </c>
       <c r="B2" t="n">
-        <v>91928</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>401779</v>
+        <v>401771</v>
       </c>
       <c r="R2" t="n">
-        <v>7045486</v>
+        <v>7045463</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -741,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131950773</v>
+        <v>131949850</v>
       </c>
       <c r="B3" t="n">
-        <v>80433</v>
+        <v>91929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,23 +793,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401771</v>
+        <v>401779</v>
       </c>
       <c r="R3" t="n">
-        <v>7045463</v>
+        <v>7045486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,7 +848,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131952947</v>
+        <v>131952934</v>
       </c>
       <c r="B11" t="n">
-        <v>80433</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401736</v>
+        <v>401733</v>
       </c>
       <c r="R11" t="n">
-        <v>7045554</v>
+        <v>7045548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1719,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131952934</v>
+        <v>131952947</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,21 +1762,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1786,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401733</v>
+        <v>401736</v>
       </c>
       <c r="R12" t="n">
-        <v>7045548</v>
+        <v>7045554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1821,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1826,12 +1831,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 15371-2026 artfynd.xlsx
+++ b/artfynd/A 15371-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131950773</v>
+        <v>131949493</v>
       </c>
       <c r="B2" t="n">
-        <v>80433</v>
+        <v>80489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>401771</v>
+        <v>401759</v>
       </c>
       <c r="R2" t="n">
-        <v>7045463</v>
+        <v>7045486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131949850</v>
+        <v>131950773</v>
       </c>
       <c r="B3" t="n">
-        <v>91929</v>
+        <v>80489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,19 +793,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -813,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401779</v>
+        <v>401771</v>
       </c>
       <c r="R3" t="n">
-        <v>7045486</v>
+        <v>7045463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -858,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131959466</v>
+        <v>131952947</v>
       </c>
       <c r="B4" t="n">
-        <v>80433</v>
+        <v>80489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,7 +927,7 @@
         <v>401736</v>
       </c>
       <c r="R4" t="n">
-        <v>7045540</v>
+        <v>7045554</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -965,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131949493</v>
+        <v>131953014</v>
       </c>
       <c r="B5" t="n">
-        <v>80433</v>
+        <v>80489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401759</v>
+        <v>401739</v>
       </c>
       <c r="R5" t="n">
-        <v>7045486</v>
+        <v>7045526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131949502</v>
+        <v>131953083</v>
       </c>
       <c r="B6" t="n">
-        <v>80432</v>
+        <v>80489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401764</v>
+        <v>401736</v>
       </c>
       <c r="R6" t="n">
-        <v>7045490</v>
+        <v>7045540</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131953014</v>
+        <v>131949502</v>
       </c>
       <c r="B7" t="n">
-        <v>80433</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>401739</v>
+        <v>401764</v>
       </c>
       <c r="R7" t="n">
-        <v>7045526</v>
+        <v>7045490</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,27 +1317,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131950316</v>
+        <v>131951700</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1344,14 +1348,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
+          <t>Lill-Rörsvallen, Kall, Lill-Rörsvallen, Kall, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401786</v>
+        <v>401805</v>
       </c>
       <c r="R8" t="n">
-        <v>7045470</v>
+        <v>7045391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1393,12 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,11 +1427,11 @@
         <v>131951992</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1532,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131951700</v>
+        <v>131950316</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1543,16 +1542,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1563,14 +1562,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Rörsvallen, Kall, Lill-Rörsvallen, Kall, Jmt</t>
+          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401805</v>
+        <v>401786</v>
       </c>
       <c r="R10" t="n">
-        <v>7045391</v>
+        <v>7045470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1612,7 +1611,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131952934</v>
+        <v>131952639</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401733</v>
+        <v>401730</v>
       </c>
       <c r="R11" t="n">
-        <v>7045548</v>
+        <v>7045567</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1751,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131952947</v>
+        <v>131952934</v>
       </c>
       <c r="B12" t="n">
-        <v>80433</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1786,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401736</v>
+        <v>401733</v>
       </c>
       <c r="R12" t="n">
-        <v>7045554</v>
+        <v>7045548</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1831,7 +1835,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,118 +1864,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>131952639</v>
-      </c>
-      <c r="B13" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Lill-Rörsvallen, Lill-Rörsvallen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>401730</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7045567</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
